--- a/Sales_Performance_Dashboard.xlsx
+++ b/Sales_Performance_Dashboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{486CBB95-F0EB-4F78-9D1D-23A4E5DB1AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4A82401-8E2C-4054-9627-2ECD6DA9552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="642" r:id="rId10"/>
+    <pivotCache cacheId="519" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -185,10 +185,10 @@
     <t>None</t>
   </si>
   <si>
-    <t>Medium</t>
+    <t>Low</t>
   </si>
   <si>
-    <t>Low</t>
+    <t>Medium</t>
   </si>
   <si>
     <t>High</t>
@@ -655,24 +655,6 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -692,6 +674,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2117,10 +2117,10 @@
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>Low</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Low</c:v>
+                  <c:v>Medium</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>High</c:v>
@@ -2138,10 +2138,10 @@
                   <c:v>0.21859650483266266</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14387469955502344</c:v>
+                  <c:v>0.17871490758328185</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.17871490758328185</c:v>
+                  <c:v>0.14387469955502344</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9.0678117031293123E-2</c:v>
@@ -4480,10 +4480,10 @@
                   <c:v>None</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Medium</c:v>
+                  <c:v>Low</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Low</c:v>
+                  <c:v>Medium</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>High</c:v>
@@ -4501,10 +4501,10 @@
                   <c:v>0.21859650483266266</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14387469955502344</c:v>
+                  <c:v>0.17871490758328185</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.17871490758328185</c:v>
+                  <c:v>0.14387469955502344</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9.0678117031293123E-2</c:v>
@@ -12381,7 +12381,7 @@
               <a:ea typeface="+mn-lt"/>
               <a:cs typeface="+mn-lt"/>
             </a:rPr>
-            <a:t>*Total sales were $118.7M with $16.9M profit (14.2% margin).</a:t>
+            <a:t>*Total sales were $11.87 cr. with $1.69 cr. profit (14.2% margin).</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -12395,7 +12395,7 @@
               <a:ea typeface="+mn-lt"/>
               <a:cs typeface="+mn-lt"/>
             </a:rPr>
-            <a:t>*Government leads, with $52.5M in sales and $11.4M in profit.</a:t>
+            <a:t>*Government leads, with $5.25  cr. in sales and $1.14 cr. in profit.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -12409,7 +12409,7 @@
               <a:ea typeface="+mn-lt"/>
               <a:cs typeface="+mn-lt"/>
             </a:rPr>
-            <a:t>*Enterprise lost $0.6M, and all 58 loss-making orders are Enterprise orders with medium or high discounts.</a:t>
+            <a:t>*Enterprise lost $6.1 lakh, and all 58 loss-making orders are Enterprise orders with medium or high discounts.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -12437,7 +12437,7 @@
               <a:ea typeface="+mn-lt"/>
               <a:cs typeface="+mn-lt"/>
             </a:rPr>
-            <a:t>*Paseo is the top product ($33.0M), and Paseo in Canada is the most profitable cell.</a:t>
+            <a:t>*Paseo is the top product ($3.30 cr.), and Paseo in Canada is the most profitable cell.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -12610,8 +12610,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6372225" y="9277350"/>
-          <a:ext cx="4581525" cy="1581150"/>
+          <a:off x="6372225" y="9210675"/>
+          <a:ext cx="4581525" cy="1533525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27313,7 +27313,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6FD2C95D-06CF-4DF5-BA91-0B4DBEAB5E69}" name="PivotTable1" cacheId="642" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6FD2C95D-06CF-4DF5-BA91-0B4DBEAB5E69}" name="PivotTable1" cacheId="519" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -27391,7 +27391,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00BD0834-F3A0-4AA4-A530-AED9D89B5A5F}" name="PivotTable2" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00BD0834-F3A0-4AA4-A530-AED9D89B5A5F}" name="PivotTable2" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="11">
   <location ref="A3:D16" firstHeaderRow="0" firstDataRow="1" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -28372,7 +28372,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5564659A-983C-474D-B461-211CA8A02E35}" name="PivotTable8" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5564659A-983C-474D-B461-211CA8A02E35}" name="PivotTable8" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="13">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
@@ -29124,7 +29124,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D75A564A-6BB1-4439-A928-7F030B338E11}" name="PivotTable9" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D75A564A-6BB1-4439-A928-7F030B338E11}" name="PivotTable9" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29815,7 +29815,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70D9B428-FCE7-4D58-965D-6B09DFE58DC3}" name="PivotTable10" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70D9B428-FCE7-4D58-965D-6B09DFE58DC3}" name="PivotTable10" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30510,13 +30510,13 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45F8DA42-A61B-4A26-B2B3-544BDE636309}" name="PivotTable6" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{45F8DA42-A61B-4A26-B2B3-544BDE636309}" name="PivotTable6" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
       <items count="5">
         <item x="0"/>
         <item x="2"/>
@@ -30524,6 +30524,15 @@
         <item x="3"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
@@ -30546,10 +30555,10 @@
       <x/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="2"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="3"/>
@@ -30646,7 +30655,139 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42732F6-58E6-4981-94AD-F0232B3BC1A1}" name="PivotTable11" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A88F409B-4F82-40C3-B9D6-C82BCC49DB0E}" name="PivotTable12" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A12:H19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="11" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="0" count="5" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+            <reference field="2" count="6" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42732F6-58E6-4981-94AD-F0232B3BC1A1}" name="PivotTable11" cacheId="519" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:H10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="16">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -30746,138 +30887,6 @@
               <x v="0"/>
             </reference>
             <reference field="1" count="5" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-            <reference field="2" count="6" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A88F409B-4F82-40C3-B9D6-C82BCC49DB0E}" name="PivotTable12" cacheId="642" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A12:H19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="1" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="11" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="0" count="5" selected="0">
               <x v="0"/>
               <x v="1"/>
               <x v="2"/>
@@ -31292,24 +31301,24 @@
       </c>
       <c r="E5" s="55"/>
       <c r="F5" s="56"/>
-      <c r="G5" s="60">
+      <c r="G5" s="67">
         <f>KPIs!B4</f>
         <v>1125806</v>
       </c>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="66">
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="60">
         <f>KPIs!B10</f>
         <v>0.14229109395685402</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="66">
+      <c r="K5" s="61"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="60">
         <f>KPIs!B11</f>
         <v>7.1954453379240793E-2</v>
       </c>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="62"/>
     </row>
     <row r="6" spans="1:16" ht="10.5" customHeight="1">
       <c r="A6" s="57"/>
@@ -31318,15 +31327,15 @@
       <c r="D6" s="57"/>
       <c r="E6" s="58"/>
       <c r="F6" s="59"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="71"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="65"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="30"/>
@@ -32341,10 +32350,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="72"/>
+      <c r="B1" s="66"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="22" t="s">
@@ -32952,25 +32961,25 @@
         <v>45</v>
       </c>
       <c r="B5" s="21">
-        <v>379698.5</v>
+        <v>261858.5</v>
       </c>
       <c r="C5" s="20">
-        <v>38780430.835000038</v>
+        <v>34629778.699999996</v>
       </c>
       <c r="D5" s="20">
-        <v>5579522.8349999972</v>
+        <v>6188857.7000000011</v>
       </c>
       <c r="E5" s="26">
         <f t="shared" ref="E5:E8" si="0">D5/C5</f>
-        <v>0.14387469955502344</v>
+        <v>0.17871490758328185</v>
       </c>
       <c r="G5" s="37" t="str">
         <f>A5</f>
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="H5" s="38">
         <f t="shared" ref="H5:H7" si="1">E5</f>
-        <v>0.14387469955502344</v>
+        <v>0.17871490758328185</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -32978,25 +32987,25 @@
         <v>46</v>
       </c>
       <c r="B6" s="21">
-        <v>261858.5</v>
+        <v>379698.5</v>
       </c>
       <c r="C6" s="20">
-        <v>34629778.699999996</v>
+        <v>38780430.835000038</v>
       </c>
       <c r="D6" s="20">
-        <v>6188857.7000000011</v>
+        <v>5579522.8349999972</v>
       </c>
       <c r="E6" s="26">
         <f t="shared" si="0"/>
-        <v>0.17871490758328185</v>
+        <v>0.14387469955502344</v>
       </c>
       <c r="G6" s="37" t="str">
         <f>A6</f>
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="H6" s="38">
         <f t="shared" si="1"/>
-        <v>0.17871490758328185</v>
+        <v>0.14387469955502344</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -36364,7 +36373,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" s="2">
         <v>3945</v>
@@ -36417,7 +36426,7 @@
         <v>10</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E56" s="2">
         <v>2296</v>
@@ -36470,7 +36479,7 @@
         <v>10</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E57" s="2">
         <v>1030</v>
@@ -36523,7 +36532,7 @@
         <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="2">
         <v>639</v>
@@ -36576,7 +36585,7 @@
         <v>12</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="2">
         <v>1326</v>
@@ -36629,7 +36638,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="2">
         <v>1858</v>
@@ -36682,7 +36691,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E61" s="2">
         <v>1210</v>
@@ -36735,7 +36744,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E62" s="2">
         <v>2529</v>
@@ -36788,7 +36797,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E63" s="2">
         <v>1445</v>
@@ -36841,7 +36850,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E64" s="2">
         <v>330</v>
@@ -36894,7 +36903,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E65" s="2">
         <v>2671</v>
@@ -36947,7 +36956,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E66" s="2">
         <v>766</v>
@@ -37000,7 +37009,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E67" s="2">
         <v>494</v>
@@ -37053,7 +37062,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E68" s="2">
         <v>1397</v>
@@ -37106,7 +37115,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E69" s="2">
         <v>2155</v>
@@ -37159,7 +37168,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E70" s="2">
         <v>2214</v>
@@ -37212,7 +37221,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E71" s="2">
         <v>2301</v>
@@ -37265,7 +37274,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E72" s="2">
         <v>1375.5</v>
@@ -37318,7 +37327,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E73" s="2">
         <v>1830</v>
@@ -37371,7 +37380,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E74" s="2">
         <v>2498</v>
@@ -37424,7 +37433,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E75" s="2">
         <v>663</v>
@@ -37477,7 +37486,7 @@
         <v>10</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E76" s="2">
         <v>1514</v>
@@ -37530,7 +37539,7 @@
         <v>10</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E77" s="2">
         <v>4492.5</v>
@@ -37583,7 +37592,7 @@
         <v>10</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E78" s="2">
         <v>727</v>
@@ -37636,7 +37645,7 @@
         <v>10</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E79" s="2">
         <v>787</v>
@@ -37689,7 +37698,7 @@
         <v>10</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E80" s="2">
         <v>1823</v>
@@ -37742,7 +37751,7 @@
         <v>10</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E81" s="2">
         <v>747</v>
@@ -37795,7 +37804,7 @@
         <v>10</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E82" s="2">
         <v>766</v>
@@ -37848,7 +37857,7 @@
         <v>10</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E83" s="2">
         <v>2905</v>
@@ -37901,7 +37910,7 @@
         <v>10</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E84" s="2">
         <v>2155</v>
@@ -37954,7 +37963,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E85" s="2">
         <v>3864</v>
@@ -38007,7 +38016,7 @@
         <v>11</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E86" s="2">
         <v>362</v>
@@ -38060,7 +38069,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E87" s="2">
         <v>923</v>
@@ -38113,7 +38122,7 @@
         <v>11</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E88" s="2">
         <v>663</v>
@@ -38166,7 +38175,7 @@
         <v>11</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E89" s="2">
         <v>2092</v>
@@ -38219,7 +38228,7 @@
         <v>12</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E90" s="2">
         <v>263</v>
@@ -38272,7 +38281,7 @@
         <v>12</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E91" s="2">
         <v>943.5</v>
@@ -38325,7 +38334,7 @@
         <v>12</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E92" s="2">
         <v>727</v>
@@ -38378,7 +38387,7 @@
         <v>12</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E93" s="2">
         <v>787</v>
@@ -38431,7 +38440,7 @@
         <v>12</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E94" s="2">
         <v>986</v>
@@ -38484,7 +38493,7 @@
         <v>12</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E95" s="2">
         <v>494</v>
@@ -38537,7 +38546,7 @@
         <v>12</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E96" s="2">
         <v>1397</v>
@@ -38590,7 +38599,7 @@
         <v>12</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E97" s="2">
         <v>1744</v>
@@ -38643,7 +38652,7 @@
         <v>7</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E98" s="2">
         <v>1989</v>
@@ -38696,7 +38705,7 @@
         <v>7</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E99" s="2">
         <v>321</v>
@@ -38749,7 +38758,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E100" s="2">
         <v>742.5</v>
@@ -38802,7 +38811,7 @@
         <v>8</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E101" s="2">
         <v>1295</v>
@@ -38855,7 +38864,7 @@
         <v>8</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E102" s="2">
         <v>214</v>
@@ -38908,7 +38917,7 @@
         <v>8</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E103" s="2">
         <v>2145</v>
@@ -38961,7 +38970,7 @@
         <v>8</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E104" s="2">
         <v>2852</v>
@@ -39014,7 +39023,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E105" s="2">
         <v>1142</v>
@@ -39067,7 +39076,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E106" s="2">
         <v>1566</v>
@@ -39120,7 +39129,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E107" s="2">
         <v>690</v>
@@ -39173,7 +39182,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E108" s="2">
         <v>1660</v>
@@ -39226,7 +39235,7 @@
         <v>10</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E109" s="2">
         <v>2363</v>
@@ -39279,7 +39288,7 @@
         <v>10</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E110" s="2">
         <v>918</v>
@@ -39332,7 +39341,7 @@
         <v>10</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E111" s="2">
         <v>1728</v>
@@ -39385,7 +39394,7 @@
         <v>10</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E112" s="2">
         <v>1142</v>
@@ -39438,7 +39447,7 @@
         <v>10</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E113" s="2">
         <v>662</v>
@@ -39491,7 +39500,7 @@
         <v>10</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E114" s="2">
         <v>1295</v>
@@ -39544,7 +39553,7 @@
         <v>10</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E115" s="2">
         <v>809</v>
@@ -39597,7 +39606,7 @@
         <v>10</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E116" s="2">
         <v>2145</v>
@@ -39650,7 +39659,7 @@
         <v>10</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E117" s="2">
         <v>1785</v>
@@ -39703,7 +39712,7 @@
         <v>10</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E118" s="2">
         <v>1916</v>
@@ -39756,7 +39765,7 @@
         <v>10</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E119" s="2">
         <v>2852</v>
@@ -39809,7 +39818,7 @@
         <v>10</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E120" s="2">
         <v>2729</v>
@@ -39862,7 +39871,7 @@
         <v>10</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E121" s="2">
         <v>1925</v>
@@ -39915,7 +39924,7 @@
         <v>10</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E122" s="2">
         <v>2013</v>
@@ -39968,7 +39977,7 @@
         <v>10</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E123" s="2">
         <v>1055</v>
@@ -40021,7 +40030,7 @@
         <v>10</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E124" s="2">
         <v>1084</v>
@@ -40074,7 +40083,7 @@
         <v>11</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E125" s="2">
         <v>1566</v>
@@ -40127,7 +40136,7 @@
         <v>11</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E126" s="2">
         <v>2966</v>
@@ -40180,7 +40189,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E127" s="2">
         <v>2877</v>
@@ -40233,7 +40242,7 @@
         <v>11</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E128" s="2">
         <v>809</v>
@@ -40286,7 +40295,7 @@
         <v>11</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E129" s="2">
         <v>2145</v>
@@ -40339,7 +40348,7 @@
         <v>11</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E130" s="2">
         <v>1055</v>
@@ -40392,7 +40401,7 @@
         <v>11</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E131" s="2">
         <v>544</v>
@@ -40445,7 +40454,7 @@
         <v>11</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E132" s="2">
         <v>1084</v>
@@ -40498,7 +40507,7 @@
         <v>12</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E133" s="2">
         <v>662</v>
@@ -40551,7 +40560,7 @@
         <v>12</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E134" s="2">
         <v>214</v>
@@ -40604,7 +40613,7 @@
         <v>12</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E135" s="2">
         <v>2877</v>
@@ -40657,7 +40666,7 @@
         <v>12</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E136" s="2">
         <v>2729</v>
@@ -40710,7 +40719,7 @@
         <v>12</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E137" s="2">
         <v>266</v>
@@ -40763,7 +40772,7 @@
         <v>12</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E138" s="2">
         <v>1940</v>
@@ -40816,7 +40825,7 @@
         <v>7</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E139" s="2">
         <v>259</v>
@@ -40869,7 +40878,7 @@
         <v>7</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E140" s="2">
         <v>1101</v>
@@ -40922,7 +40931,7 @@
         <v>7</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E141" s="2">
         <v>2276</v>
@@ -40975,7 +40984,7 @@
         <v>7</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E142" s="2">
         <v>2966</v>
@@ -41028,7 +41037,7 @@
         <v>7</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E143" s="2">
         <v>1236</v>
@@ -41081,7 +41090,7 @@
         <v>7</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E144" s="2">
         <v>941</v>
@@ -41134,7 +41143,7 @@
         <v>7</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E145" s="2">
         <v>1916</v>
@@ -41187,7 +41196,7 @@
         <v>8</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E146" s="2">
         <v>4243.5</v>
@@ -41240,7 +41249,7 @@
         <v>8</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E147" s="2">
         <v>2580</v>
@@ -41293,7 +41302,7 @@
         <v>8</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E148" s="2">
         <v>689</v>
@@ -41346,7 +41355,7 @@
         <v>8</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E149" s="2">
         <v>1947</v>
@@ -41399,7 +41408,7 @@
         <v>8</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E150" s="2">
         <v>908</v>
@@ -41452,7 +41461,7 @@
         <v>9</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E151" s="2">
         <v>1958</v>
@@ -41505,7 +41514,7 @@
         <v>9</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E152" s="2">
         <v>1901</v>
@@ -41558,7 +41567,7 @@
         <v>9</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E153" s="2">
         <v>544</v>
@@ -41611,7 +41620,7 @@
         <v>9</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E154" s="2">
         <v>1797</v>
@@ -41664,7 +41673,7 @@
         <v>9</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E155" s="2">
         <v>1287</v>
@@ -41717,7 +41726,7 @@
         <v>9</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E156" s="2">
         <v>1706</v>
@@ -41770,7 +41779,7 @@
         <v>10</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E157" s="2">
         <v>2434.5</v>
@@ -41823,7 +41832,7 @@
         <v>10</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E158" s="2">
         <v>1774</v>
@@ -41876,7 +41885,7 @@
         <v>10</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E159" s="2">
         <v>1901</v>
@@ -41929,7 +41938,7 @@
         <v>10</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E160" s="2">
         <v>689</v>
@@ -41982,7 +41991,7 @@
         <v>10</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E161" s="2">
         <v>1570</v>
@@ -42035,7 +42044,7 @@
         <v>10</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E162" s="2">
         <v>1369.5</v>
@@ -42088,7 +42097,7 @@
         <v>10</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E163" s="2">
         <v>2009</v>
@@ -42141,7 +42150,7 @@
         <v>10</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E164" s="2">
         <v>1945</v>
@@ -42194,7 +42203,7 @@
         <v>10</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E165" s="2">
         <v>1287</v>
@@ -42247,7 +42256,7 @@
         <v>10</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E166" s="2">
         <v>1706</v>
@@ -42300,7 +42309,7 @@
         <v>11</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E167" s="2">
         <v>2009</v>
@@ -42353,7 +42362,7 @@
         <v>12</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E168" s="2">
         <v>2844</v>
@@ -42406,7 +42415,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E169" s="2">
         <v>1916</v>
@@ -42459,7 +42468,7 @@
         <v>12</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E170" s="2">
         <v>1570</v>
@@ -42512,7 +42521,7 @@
         <v>12</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E171" s="2">
         <v>1874</v>
@@ -42565,7 +42574,7 @@
         <v>12</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E172" s="2">
         <v>1642</v>
@@ -42618,7 +42627,7 @@
         <v>12</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E173" s="2">
         <v>1945</v>
@@ -42671,7 +42680,7 @@
         <v>8</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E174" s="2">
         <v>831</v>
@@ -42724,7 +42733,7 @@
         <v>10</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E175" s="2">
         <v>1760</v>
@@ -42777,7 +42786,7 @@
         <v>11</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E176" s="2">
         <v>3850.5</v>
@@ -42830,7 +42839,7 @@
         <v>12</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E177" s="2">
         <v>2479</v>
@@ -42883,7 +42892,7 @@
         <v>9</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E178" s="2">
         <v>2031</v>
@@ -42936,7 +42945,7 @@
         <v>10</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E179" s="2">
         <v>2031</v>
@@ -42989,7 +42998,7 @@
         <v>10</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E180" s="2">
         <v>2261</v>
@@ -43042,7 +43051,7 @@
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E181" s="2">
         <v>736</v>
@@ -43095,7 +43104,7 @@
         <v>8</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E182" s="2">
         <v>2851</v>
@@ -43148,7 +43157,7 @@
         <v>8</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E183" s="2">
         <v>2021</v>
@@ -43201,7 +43210,7 @@
         <v>8</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E184" s="2">
         <v>274</v>
@@ -43254,7 +43263,7 @@
         <v>9</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E185" s="2">
         <v>1967</v>
@@ -43307,7 +43316,7 @@
         <v>9</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E186" s="2">
         <v>1859</v>
@@ -43360,7 +43369,7 @@
         <v>9</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E187" s="2">
         <v>2851</v>
@@ -43413,7 +43422,7 @@
         <v>9</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E188" s="2">
         <v>2021</v>
@@ -43466,7 +43475,7 @@
         <v>9</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E189" s="2">
         <v>1138</v>
@@ -43519,7 +43528,7 @@
         <v>10</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E190" s="2">
         <v>4251</v>
@@ -43572,7 +43581,7 @@
         <v>10</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E191" s="2">
         <v>795</v>
@@ -43625,7 +43634,7 @@
         <v>10</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E192" s="2">
         <v>1414.5</v>
@@ -43678,7 +43687,7 @@
         <v>10</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E193" s="2">
         <v>2918</v>
@@ -43731,7 +43740,7 @@
         <v>10</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E194" s="2">
         <v>3450</v>
@@ -43784,7 +43793,7 @@
         <v>10</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E195" s="2">
         <v>2988</v>
@@ -43837,7 +43846,7 @@
         <v>10</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E196" s="2">
         <v>218</v>
@@ -43890,7 +43899,7 @@
         <v>10</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E197" s="2">
         <v>2074</v>
@@ -43943,7 +43952,7 @@
         <v>10</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E198" s="2">
         <v>1056</v>
@@ -43996,7 +44005,7 @@
         <v>10</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E199" s="2">
         <v>671</v>
@@ -44049,7 +44058,7 @@
         <v>10</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E200" s="2">
         <v>1514</v>
@@ -44102,7 +44111,7 @@
         <v>10</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E201" s="2">
         <v>274</v>
@@ -44155,7 +44164,7 @@
         <v>10</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E202" s="2">
         <v>1138</v>
@@ -44208,7 +44217,7 @@
         <v>11</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E203" s="2">
         <v>1465</v>
@@ -44261,7 +44270,7 @@
         <v>11</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E204" s="2">
         <v>2646</v>
@@ -44314,7 +44323,7 @@
         <v>11</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E205" s="2">
         <v>2177</v>
@@ -44367,7 +44376,7 @@
         <v>12</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E206" s="2">
         <v>866</v>
@@ -44420,7 +44429,7 @@
         <v>12</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E207" s="2">
         <v>349</v>
@@ -44473,7 +44482,7 @@
         <v>12</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E208" s="2">
         <v>2177</v>
@@ -44526,7 +44535,7 @@
         <v>12</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E209" s="2">
         <v>1514</v>
@@ -44579,7 +44588,7 @@
         <v>7</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E210" s="2">
         <v>1865</v>
@@ -44632,7 +44641,7 @@
         <v>7</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E211" s="2">
         <v>1074</v>
@@ -44685,7 +44694,7 @@
         <v>7</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E212" s="2">
         <v>1907</v>
@@ -44738,7 +44747,7 @@
         <v>7</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E213" s="2">
         <v>671</v>
@@ -44791,7 +44800,7 @@
         <v>7</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E214" s="2">
         <v>1778</v>
@@ -44844,7 +44853,7 @@
         <v>9</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E215" s="2">
         <v>1159</v>
@@ -44897,7 +44906,7 @@
         <v>10</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E216" s="2">
         <v>1372</v>
@@ -44950,7 +44959,7 @@
         <v>10</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E217" s="2">
         <v>2349</v>
@@ -45003,7 +45012,7 @@
         <v>10</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E218" s="2">
         <v>2689</v>
@@ -45056,7 +45065,7 @@
         <v>10</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E219" s="2">
         <v>2431</v>
@@ -45109,7 +45118,7 @@
         <v>11</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E220" s="2">
         <v>2431</v>
@@ -45162,7 +45171,7 @@
         <v>12</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E221" s="2">
         <v>2689</v>
@@ -45215,7 +45224,7 @@
         <v>7</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E222" s="2">
         <v>1683</v>
@@ -45268,7 +45277,7 @@
         <v>7</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E223" s="2">
         <v>1123</v>
@@ -45321,7 +45330,7 @@
         <v>7</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E224" s="2">
         <v>1159</v>
@@ -45374,7 +45383,7 @@
         <v>8</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E225" s="2">
         <v>1865</v>
@@ -45427,7 +45436,7 @@
         <v>8</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E226" s="2">
         <v>1116</v>
@@ -45480,7 +45489,7 @@
         <v>8</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E227" s="2">
         <v>1563</v>
@@ -45533,7 +45542,7 @@
         <v>8</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E228" s="2">
         <v>991</v>
@@ -45586,7 +45595,7 @@
         <v>8</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E229" s="2">
         <v>1016</v>
@@ -45639,7 +45648,7 @@
         <v>8</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E230" s="2">
         <v>2791</v>
@@ -45692,7 +45701,7 @@
         <v>8</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E231" s="2">
         <v>570</v>
@@ -45745,7 +45754,7 @@
         <v>8</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E232" s="2">
         <v>2487</v>
@@ -45798,7 +45807,7 @@
         <v>9</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E233" s="2">
         <v>1384.5</v>
@@ -45851,7 +45860,7 @@
         <v>9</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E234" s="2">
         <v>3627</v>
@@ -45904,7 +45913,7 @@
         <v>9</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E235" s="2">
         <v>720</v>
@@ -45957,7 +45966,7 @@
         <v>9</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E236" s="2">
         <v>2342</v>
@@ -46010,7 +46019,7 @@
         <v>9</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E237" s="2">
         <v>1100</v>
@@ -46063,7 +46072,7 @@
         <v>10</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E238" s="2">
         <v>1303</v>
@@ -46116,7 +46125,7 @@
         <v>10</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E239" s="2">
         <v>2992</v>
@@ -46169,7 +46178,7 @@
         <v>10</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E240" s="2">
         <v>2385</v>
@@ -46222,7 +46231,7 @@
         <v>10</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E241" s="2">
         <v>1607</v>
@@ -46275,7 +46284,7 @@
         <v>10</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E242" s="2">
         <v>2327</v>
@@ -46328,7 +46337,7 @@
         <v>10</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E243" s="2">
         <v>991</v>
@@ -46381,7 +46390,7 @@
         <v>10</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E244" s="2">
         <v>602</v>
@@ -46434,7 +46443,7 @@
         <v>10</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E245" s="2">
         <v>2620</v>
@@ -46487,7 +46496,7 @@
         <v>10</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E246" s="2">
         <v>1228</v>
@@ -46540,7 +46549,7 @@
         <v>10</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E247" s="2">
         <v>1389</v>
@@ -46593,7 +46602,7 @@
         <v>10</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E248" s="2">
         <v>861</v>
@@ -46646,7 +46655,7 @@
         <v>10</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E249" s="2">
         <v>704</v>
@@ -46699,7 +46708,7 @@
         <v>10</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E250" s="2">
         <v>1802</v>
@@ -46752,7 +46761,7 @@
         <v>10</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E251" s="2">
         <v>2663</v>
@@ -46805,7 +46814,7 @@
         <v>10</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E252" s="2">
         <v>2136</v>
@@ -46858,7 +46867,7 @@
         <v>10</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E253" s="2">
         <v>2116</v>
@@ -46911,7 +46920,7 @@
         <v>11</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E254" s="2">
         <v>555</v>
@@ -46964,7 +46973,7 @@
         <v>11</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E255" s="2">
         <v>2861</v>
@@ -47017,7 +47026,7 @@
         <v>11</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E256" s="2">
         <v>807</v>
@@ -47070,7 +47079,7 @@
         <v>11</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E257" s="2">
         <v>602</v>
@@ -47123,7 +47132,7 @@
         <v>11</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E258" s="2">
         <v>2832</v>
@@ -47176,7 +47185,7 @@
         <v>11</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E259" s="2">
         <v>1579</v>
@@ -47229,7 +47238,7 @@
         <v>11</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E260" s="2">
         <v>861</v>
@@ -47282,7 +47291,7 @@
         <v>11</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E261" s="2">
         <v>704</v>
@@ -47335,7 +47344,7 @@
         <v>11</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E262" s="2">
         <v>1033</v>
@@ -47388,7 +47397,7 @@
         <v>11</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E263" s="2">
         <v>1250</v>
@@ -47441,7 +47450,7 @@
         <v>12</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E264" s="2">
         <v>1389</v>
@@ -47494,7 +47503,7 @@
         <v>12</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E265" s="2">
         <v>1265</v>
@@ -47547,7 +47556,7 @@
         <v>12</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E266" s="2">
         <v>2297</v>
@@ -47600,7 +47609,7 @@
         <v>12</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E267" s="2">
         <v>2663</v>
@@ -47653,7 +47662,7 @@
         <v>12</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E268" s="2">
         <v>570</v>
@@ -47706,7 +47715,7 @@
         <v>12</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E269" s="2">
         <v>2487</v>
@@ -47759,7 +47768,7 @@
         <v>7</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E270" s="2">
         <v>1350</v>
@@ -47812,7 +47821,7 @@
         <v>7</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E271" s="2">
         <v>552</v>
@@ -47865,7 +47874,7 @@
         <v>7</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E272" s="2">
         <v>1228</v>
@@ -47918,7 +47927,7 @@
         <v>7</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E273" s="2">
         <v>1250</v>
@@ -47971,7 +47980,7 @@
         <v>10</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E274" s="2">
         <v>3801</v>
@@ -48024,7 +48033,7 @@
         <v>8</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E275" s="2">
         <v>1117.5</v>
@@ -48077,7 +48086,7 @@
         <v>8</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E276" s="2">
         <v>2844</v>
@@ -48130,7 +48139,7 @@
         <v>8</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E277" s="2">
         <v>562</v>
@@ -48183,7 +48192,7 @@
         <v>8</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E278" s="2">
         <v>2299</v>
@@ -48236,7 +48245,7 @@
         <v>8</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E279" s="2">
         <v>2030</v>
@@ -48289,7 +48298,7 @@
         <v>8</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E280" s="2">
         <v>263</v>
@@ -48342,7 +48351,7 @@
         <v>8</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E281" s="2">
         <v>887</v>
@@ -48395,7 +48404,7 @@
         <v>9</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E282" s="2">
         <v>980</v>
@@ -48448,7 +48457,7 @@
         <v>9</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E283" s="2">
         <v>1460</v>
@@ -48501,7 +48510,7 @@
         <v>9</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E284" s="2">
         <v>1403</v>
@@ -48554,7 +48563,7 @@
         <v>9</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E285" s="2">
         <v>2723</v>
@@ -48607,7 +48616,7 @@
         <v>10</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E286" s="2">
         <v>1496</v>
@@ -48660,7 +48669,7 @@
         <v>10</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E287" s="2">
         <v>2299</v>
@@ -48713,7 +48722,7 @@
         <v>10</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E288" s="2">
         <v>727</v>
@@ -48766,7 +48775,7 @@
         <v>11</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E289" s="2">
         <v>952</v>
@@ -48819,7 +48828,7 @@
         <v>11</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E290" s="2">
         <v>2755</v>
@@ -48872,7 +48881,7 @@
         <v>11</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E291" s="2">
         <v>1530</v>
@@ -48925,7 +48934,7 @@
         <v>11</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E292" s="2">
         <v>1496</v>
@@ -48978,7 +48987,7 @@
         <v>11</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E293" s="2">
         <v>1498</v>
@@ -49031,7 +49040,7 @@
         <v>11</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E294" s="2">
         <v>1221</v>
@@ -49084,7 +49093,7 @@
         <v>11</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E295" s="2">
         <v>2076</v>
@@ -49137,7 +49146,7 @@
         <v>12</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E296" s="2">
         <v>2844</v>
@@ -49190,7 +49199,7 @@
         <v>12</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E297" s="2">
         <v>1498</v>
@@ -49243,7 +49252,7 @@
         <v>12</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E298" s="2">
         <v>1221</v>
@@ -49296,7 +49305,7 @@
         <v>12</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E299" s="2">
         <v>1123</v>
@@ -49349,7 +49358,7 @@
         <v>12</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E300" s="2">
         <v>2436</v>
@@ -49402,7 +49411,7 @@
         <v>7</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E301" s="2">
         <v>1987.5</v>
@@ -49455,7 +49464,7 @@
         <v>7</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E302" s="2">
         <v>1679</v>
@@ -49508,7 +49517,7 @@
         <v>7</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E303" s="2">
         <v>727</v>
@@ -49561,7 +49570,7 @@
         <v>7</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E304" s="2">
         <v>1403</v>
@@ -49614,7 +49623,7 @@
         <v>7</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E305" s="2">
         <v>2076</v>
@@ -49667,7 +49676,7 @@
         <v>9</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E306" s="2">
         <v>1757</v>
@@ -49720,7 +49729,7 @@
         <v>10</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E307" s="2">
         <v>2198</v>
@@ -49773,7 +49782,7 @@
         <v>10</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E308" s="2">
         <v>1743</v>
@@ -49826,7 +49835,7 @@
         <v>10</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E309" s="2">
         <v>1153</v>
@@ -49879,7 +49888,7 @@
         <v>10</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E310" s="2">
         <v>1757</v>
@@ -49932,7 +49941,7 @@
         <v>11</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E311" s="2">
         <v>1001</v>
@@ -49985,7 +49994,7 @@
         <v>11</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E312" s="2">
         <v>1333</v>
@@ -50038,7 +50047,7 @@
         <v>12</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E313" s="2">
         <v>1153</v>
@@ -50091,7 +50100,7 @@
         <v>8</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E314" s="2">
         <v>727</v>
@@ -50144,7 +50153,7 @@
         <v>8</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E315" s="2">
         <v>1884</v>
@@ -50197,7 +50206,7 @@
         <v>8</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E316" s="2">
         <v>1834</v>
@@ -50250,7 +50259,7 @@
         <v>9</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E317" s="2">
         <v>2340</v>
@@ -50303,7 +50312,7 @@
         <v>9</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E318" s="2">
         <v>2342</v>
@@ -50356,7 +50365,7 @@
         <v>10</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E319" s="2">
         <v>1031</v>
@@ -50409,7 +50418,7 @@
         <v>11</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E320" s="2">
         <v>1262</v>
@@ -50462,7 +50471,7 @@
         <v>11</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E321" s="2">
         <v>1135</v>
@@ -50515,7 +50524,7 @@
         <v>11</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E322" s="2">
         <v>547</v>
@@ -50568,7 +50577,7 @@
         <v>11</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E323" s="2">
         <v>1582</v>
@@ -50621,7 +50630,7 @@
         <v>12</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E324" s="2">
         <v>1738.5</v>
@@ -50674,7 +50683,7 @@
         <v>12</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E325" s="2">
         <v>2215</v>
@@ -50727,7 +50736,7 @@
         <v>12</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E326" s="2">
         <v>1582</v>
@@ -50780,7 +50789,7 @@
         <v>7</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E327" s="2">
         <v>1135</v>
@@ -50833,7 +50842,7 @@
         <v>8</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E328" s="2">
         <v>1761</v>
@@ -50886,7 +50895,7 @@
         <v>8</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E329" s="2">
         <v>448</v>
@@ -50939,7 +50948,7 @@
         <v>8</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E330" s="2">
         <v>2181</v>
@@ -50992,7 +51001,7 @@
         <v>9</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E331" s="2">
         <v>1976</v>
@@ -51045,7 +51054,7 @@
         <v>9</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E332" s="2">
         <v>2181</v>
@@ -51098,7 +51107,7 @@
         <v>9</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E333" s="2">
         <v>2500</v>
@@ -51151,7 +51160,7 @@
         <v>10</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E334" s="2">
         <v>1702</v>
@@ -51204,7 +51213,7 @@
         <v>10</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E335" s="2">
         <v>448</v>
@@ -51257,7 +51266,7 @@
         <v>10</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E336" s="2">
         <v>3513</v>
@@ -51310,7 +51319,7 @@
         <v>10</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E337" s="2">
         <v>2101</v>
@@ -51363,7 +51372,7 @@
         <v>10</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E338" s="2">
         <v>2931</v>
@@ -51416,7 +51425,7 @@
         <v>10</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E339" s="2">
         <v>1535</v>
@@ -51469,7 +51478,7 @@
         <v>10</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E340" s="2">
         <v>1123</v>
@@ -51522,7 +51531,7 @@
         <v>10</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E341" s="2">
         <v>1404</v>
@@ -51575,7 +51584,7 @@
         <v>10</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E342" s="2">
         <v>2763</v>
@@ -51628,7 +51637,7 @@
         <v>10</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E343" s="2">
         <v>2125</v>
@@ -51681,7 +51690,7 @@
         <v>11</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E344" s="2">
         <v>1659</v>
@@ -51734,7 +51743,7 @@
         <v>11</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E345" s="2">
         <v>609</v>
@@ -51787,7 +51796,7 @@
         <v>11</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E346" s="2">
         <v>2087</v>
@@ -51840,7 +51849,7 @@
         <v>11</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E347" s="2">
         <v>1976</v>
@@ -51893,7 +51902,7 @@
         <v>11</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E348" s="2">
         <v>1421</v>
@@ -51946,7 +51955,7 @@
         <v>11</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E349" s="2">
         <v>1372</v>
@@ -51999,7 +52008,7 @@
         <v>11</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E350" s="2">
         <v>588</v>
@@ -52052,7 +52061,7 @@
         <v>12</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E351" s="2">
         <v>3244.5</v>
@@ -52105,7 +52114,7 @@
         <v>12</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E352" s="2">
         <v>959</v>
@@ -52158,7 +52167,7 @@
         <v>12</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E353" s="2">
         <v>2747</v>
@@ -52211,7 +52220,7 @@
         <v>7</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E354" s="2">
         <v>1645</v>
@@ -52264,7 +52273,7 @@
         <v>7</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E355" s="2">
         <v>2876</v>
@@ -52317,7 +52326,7 @@
         <v>7</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E356" s="2">
         <v>994</v>
@@ -52370,7 +52379,7 @@
         <v>7</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E357" s="2">
         <v>1118</v>
@@ -52423,7 +52432,7 @@
         <v>7</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E358" s="2">
         <v>1372</v>
@@ -52476,7 +52485,7 @@
         <v>9</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E359" s="2">
         <v>488</v>
@@ -52529,7 +52538,7 @@
         <v>9</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E360" s="2">
         <v>1282</v>
@@ -52582,7 +52591,7 @@
         <v>10</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E361" s="2">
         <v>257</v>
@@ -52635,7 +52644,7 @@
         <v>7</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E362" s="2">
         <v>1282</v>
@@ -52688,7 +52697,7 @@
         <v>8</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E363" s="2">
         <v>1540</v>
@@ -52741,7 +52750,7 @@
         <v>8</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E364" s="2">
         <v>490</v>
@@ -52794,7 +52803,7 @@
         <v>8</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E365" s="2">
         <v>1362</v>
@@ -52847,7 +52856,7 @@
         <v>9</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E366" s="2">
         <v>2501</v>
@@ -52900,7 +52909,7 @@
         <v>9</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E367" s="2">
         <v>708</v>
@@ -52953,7 +52962,7 @@
         <v>9</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E368" s="2">
         <v>645</v>
@@ -53006,7 +53015,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E369" s="2">
         <v>1562</v>
@@ -53059,7 +53068,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E370" s="2">
         <v>1283</v>
@@ -53112,7 +53121,7 @@
         <v>9</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E371" s="2">
         <v>711</v>
@@ -53165,7 +53174,7 @@
         <v>10</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E372" s="2">
         <v>1114</v>
@@ -53218,7 +53227,7 @@
         <v>10</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E373" s="2">
         <v>1259</v>
@@ -53271,7 +53280,7 @@
         <v>10</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E374" s="2">
         <v>1095</v>
@@ -53324,7 +53333,7 @@
         <v>10</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E375" s="2">
         <v>1366</v>
@@ -53377,7 +53386,7 @@
         <v>10</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E376" s="2">
         <v>2460</v>
@@ -53430,7 +53439,7 @@
         <v>10</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E377" s="2">
         <v>678</v>
@@ -53483,7 +53492,7 @@
         <v>10</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E378" s="2">
         <v>1598</v>
@@ -53536,7 +53545,7 @@
         <v>10</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E379" s="2">
         <v>2409</v>
@@ -53589,7 +53598,7 @@
         <v>10</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E380" s="2">
         <v>1934</v>
@@ -53642,7 +53651,7 @@
         <v>10</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E381" s="2">
         <v>2993</v>
@@ -53695,7 +53704,7 @@
         <v>10</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E382" s="2">
         <v>2146</v>
@@ -53748,7 +53757,7 @@
         <v>10</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E383" s="2">
         <v>1946</v>
@@ -53801,7 +53810,7 @@
         <v>10</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E384" s="2">
         <v>1362</v>
@@ -53854,7 +53863,7 @@
         <v>11</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E385" s="2">
         <v>598</v>
@@ -53907,7 +53916,7 @@
         <v>11</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E386" s="2">
         <v>2907</v>
@@ -53960,7 +53969,7 @@
         <v>11</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E387" s="2">
         <v>2338</v>
@@ -54013,7 +54022,7 @@
         <v>11</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E388" s="2">
         <v>386</v>
@@ -54066,7 +54075,7 @@
         <v>11</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E389" s="2">
         <v>635</v>
@@ -54119,7 +54128,7 @@
         <v>12</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E390" s="2">
         <v>574.5</v>
@@ -54172,7 +54181,7 @@
         <v>12</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E391" s="2">
         <v>2338</v>
@@ -54225,7 +54234,7 @@
         <v>12</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E392" s="2">
         <v>381</v>
@@ -54278,7 +54287,7 @@
         <v>12</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E393" s="2">
         <v>422</v>
@@ -54331,7 +54340,7 @@
         <v>12</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E394" s="2">
         <v>2134</v>
@@ -54384,7 +54393,7 @@
         <v>12</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E395" s="2">
         <v>808</v>
@@ -54437,7 +54446,7 @@
         <v>7</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E396" s="2">
         <v>708</v>
@@ -54490,7 +54499,7 @@
         <v>7</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E397" s="2">
         <v>2907</v>
@@ -54543,7 +54552,7 @@
         <v>7</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E398" s="2">
         <v>1366</v>
@@ -54596,7 +54605,7 @@
         <v>7</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E399" s="2">
         <v>2460</v>
@@ -54649,7 +54658,7 @@
         <v>7</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E400" s="2">
         <v>1520</v>
@@ -54702,7 +54711,7 @@
         <v>7</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E401" s="2">
         <v>711</v>
@@ -54755,7 +54764,7 @@
         <v>7</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E402" s="2">
         <v>1375</v>
@@ -54808,7 +54817,7 @@
         <v>7</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E403" s="2">
         <v>635</v>
@@ -54861,7 +54870,7 @@
         <v>12</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E404" s="2">
         <v>436.5</v>
@@ -54914,7 +54923,7 @@
         <v>8</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E405" s="2">
         <v>1094</v>
@@ -54967,7 +54976,7 @@
         <v>8</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E406" s="2">
         <v>367</v>
@@ -55020,7 +55029,7 @@
         <v>9</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E407" s="2">
         <v>3802.5</v>
@@ -55073,7 +55082,7 @@
         <v>9</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E408" s="2">
         <v>1666</v>
@@ -55126,7 +55135,7 @@
         <v>9</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E409" s="2">
         <v>322</v>
@@ -55179,7 +55188,7 @@
         <v>9</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E410" s="2">
         <v>2321</v>
@@ -55232,7 +55241,7 @@
         <v>9</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E411" s="2">
         <v>1857</v>
@@ -55285,7 +55294,7 @@
         <v>9</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E412" s="2">
         <v>1611</v>
@@ -55338,7 +55347,7 @@
         <v>9</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E413" s="2">
         <v>2797</v>
@@ -55391,7 +55400,7 @@
         <v>9</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E414" s="2">
         <v>334</v>
@@ -55444,7 +55453,7 @@
         <v>10</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E415" s="2">
         <v>2565</v>
@@ -55497,7 +55506,7 @@
         <v>10</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E416" s="2">
         <v>2417</v>
@@ -55550,7 +55559,7 @@
         <v>10</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E417" s="2">
         <v>3675</v>
@@ -55603,7 +55612,7 @@
         <v>10</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E418" s="2">
         <v>1094</v>
@@ -55656,7 +55665,7 @@
         <v>10</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E419" s="2">
         <v>1227</v>
@@ -55709,7 +55718,7 @@
         <v>10</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E420" s="2">
         <v>367</v>
@@ -55762,7 +55771,7 @@
         <v>10</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E421" s="2">
         <v>1324</v>
@@ -55815,7 +55824,7 @@
         <v>10</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E422" s="2">
         <v>1775</v>
@@ -55868,7 +55877,7 @@
         <v>10</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E423" s="2">
         <v>2797</v>
@@ -55921,7 +55930,7 @@
         <v>11</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E424" s="2">
         <v>245</v>
@@ -55974,7 +55983,7 @@
         <v>11</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E425" s="2">
         <v>3793.5</v>
@@ -56027,7 +56036,7 @@
         <v>11</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E426" s="2">
         <v>1307</v>
@@ -56080,7 +56089,7 @@
         <v>11</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E427" s="2">
         <v>567</v>
@@ -56133,7 +56142,7 @@
         <v>11</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E428" s="2">
         <v>2110</v>
@@ -56186,7 +56195,7 @@
         <v>11</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E429" s="2">
         <v>1269</v>
@@ -56239,7 +56248,7 @@
         <v>12</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E430" s="2">
         <v>1956</v>
@@ -56292,7 +56301,7 @@
         <v>12</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E431" s="2">
         <v>2659</v>
@@ -56345,7 +56354,7 @@
         <v>12</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E432" s="2">
         <v>1351.5</v>
@@ -56398,7 +56407,7 @@
         <v>12</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E433" s="2">
         <v>880</v>
@@ -56451,7 +56460,7 @@
         <v>12</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E434" s="2">
         <v>1867</v>
@@ -56504,7 +56513,7 @@
         <v>12</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E435" s="2">
         <v>2234</v>
@@ -56557,7 +56566,7 @@
         <v>12</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E436" s="2">
         <v>1227</v>
@@ -56610,7 +56619,7 @@
         <v>12</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E437" s="2">
         <v>877</v>
@@ -56663,7 +56672,7 @@
         <v>7</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E438" s="2">
         <v>2071</v>
@@ -56716,7 +56725,7 @@
         <v>7</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E439" s="2">
         <v>1269</v>
@@ -56769,7 +56778,7 @@
         <v>7</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E440" s="2">
         <v>970</v>
@@ -56822,7 +56831,7 @@
         <v>7</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E441" s="2">
         <v>1694</v>
@@ -56875,7 +56884,7 @@
         <v>8</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E442" s="2">
         <v>663</v>
@@ -56928,7 +56937,7 @@
         <v>8</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E443" s="2">
         <v>819</v>
@@ -56981,7 +56990,7 @@
         <v>8</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E444" s="2">
         <v>1580</v>
@@ -57034,7 +57043,7 @@
         <v>8</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E445" s="2">
         <v>521</v>
@@ -57087,7 +57096,7 @@
         <v>10</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E446" s="2">
         <v>973</v>
@@ -57140,7 +57149,7 @@
         <v>10</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E447" s="2">
         <v>1038</v>
@@ -57193,7 +57202,7 @@
         <v>10</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E448" s="2">
         <v>360</v>
@@ -57246,7 +57255,7 @@
         <v>11</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E449" s="2">
         <v>1967</v>
@@ -57299,7 +57308,7 @@
         <v>11</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E450" s="2">
         <v>2628</v>
@@ -57352,7 +57361,7 @@
         <v>12</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E451" s="2">
         <v>360</v>
@@ -57405,7 +57414,7 @@
         <v>12</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E452" s="2">
         <v>2682</v>
@@ -57458,7 +57467,7 @@
         <v>12</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E453" s="2">
         <v>521</v>
@@ -57511,7 +57520,7 @@
         <v>7</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E454" s="2">
         <v>1038</v>
@@ -57564,7 +57573,7 @@
         <v>7</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E455" s="2">
         <v>1630.5</v>
@@ -57617,7 +57626,7 @@
         <v>7</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E456" s="2">
         <v>306</v>
